--- a/data/processed/terremotos_procesados_reshape.xlsx
+++ b/data/processed/terremotos_procesados_reshape.xlsx
@@ -435,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T726"/>
+  <dimension ref="A1:T727"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -45083,7 +45083,7 @@
         <v>46290</v>
       </c>
       <c r="B721">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C721">
         <v>9</v>
@@ -45154,7 +45154,7 @@
         <v>2026</v>
       </c>
       <c r="E722">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F722">
         <v>32</v>
@@ -45190,16 +45190,16 @@
         <v>43</v>
       </c>
       <c r="Q722">
-        <v>30.66666666666667</v>
+        <v>33</v>
       </c>
       <c r="R722">
-        <v>32.2</v>
+        <v>33.6</v>
       </c>
       <c r="S722">
-        <v>30.32280814492209</v>
+        <v>33.82280814492209</v>
       </c>
       <c r="T722">
-        <v>31.61629476324428</v>
+        <v>33.94962809657761</v>
       </c>
     </row>
     <row r="723" spans="1:20">
@@ -45207,7 +45207,7 @@
         <v>46292</v>
       </c>
       <c r="B723">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C723">
         <v>9</v>
@@ -45219,7 +45219,7 @@
         <v>37</v>
       </c>
       <c r="F723">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G723">
         <v>32</v>
@@ -45252,16 +45252,16 @@
         <v>33</v>
       </c>
       <c r="Q723">
-        <v>32.33333333333334</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="R723">
-        <v>32.4</v>
+        <v>33.8</v>
       </c>
       <c r="S723">
-        <v>33.66140407246105</v>
+        <v>35.41140407246105</v>
       </c>
       <c r="T723">
-        <v>33.41086317549619</v>
+        <v>34.96641873105175</v>
       </c>
     </row>
     <row r="724" spans="1:20">
@@ -45269,7 +45269,7 @@
         <v>46293</v>
       </c>
       <c r="B724">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C724">
         <v>9</v>
@@ -45278,13 +45278,13 @@
         <v>2026</v>
       </c>
       <c r="E724">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F724">
         <v>37</v>
       </c>
       <c r="G724">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H724">
         <v>32</v>
@@ -45314,16 +45314,16 @@
         <v>34</v>
       </c>
       <c r="Q724">
-        <v>33.33333333333334</v>
+        <v>36</v>
       </c>
       <c r="R724">
-        <v>32.8</v>
+        <v>34.4</v>
       </c>
       <c r="S724">
-        <v>34.33070203623052</v>
+        <v>35.70570203623052</v>
       </c>
       <c r="T724">
-        <v>33.9405754503308</v>
+        <v>35.31094582070116</v>
       </c>
     </row>
     <row r="725" spans="1:20">
@@ -45340,16 +45340,16 @@
         <v>2026</v>
       </c>
       <c r="E725">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F725">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G725">
         <v>37</v>
       </c>
       <c r="H725">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I725">
         <v>32</v>
@@ -45376,16 +45376,16 @@
         <v>34</v>
       </c>
       <c r="Q725">
-        <v>39.33333333333334</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="R725">
-        <v>35.6</v>
+        <v>37.6</v>
       </c>
       <c r="S725">
-        <v>40.16535101811526</v>
+        <v>41.85285101811526</v>
       </c>
       <c r="T725">
-        <v>37.96038363355387</v>
+        <v>39.54063054713411</v>
       </c>
     </row>
     <row r="726" spans="1:20">
@@ -45393,7 +45393,7 @@
         <v>46295</v>
       </c>
       <c r="B726">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C726">
         <v>9</v>
@@ -45405,16 +45405,16 @@
         <v>28</v>
       </c>
       <c r="F726">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G726">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H726">
         <v>37</v>
       </c>
       <c r="I726">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J726">
         <v>32</v>
@@ -45438,16 +45438,78 @@
         <v>46</v>
       </c>
       <c r="Q726">
-        <v>36.33333333333334</v>
+        <v>37.33333333333334</v>
       </c>
       <c r="R726">
-        <v>34.8</v>
+        <v>36.8</v>
       </c>
       <c r="S726">
-        <v>34.08267550905763</v>
+        <v>34.92642550905763</v>
       </c>
       <c r="T726">
-        <v>34.64025575570258</v>
+        <v>35.69375369808941</v>
+      </c>
+    </row>
+    <row r="727" spans="1:20">
+      <c r="A727" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B727">
+        <v>30</v>
+      </c>
+      <c r="C727">
+        <v>10</v>
+      </c>
+      <c r="D727">
+        <v>2026</v>
+      </c>
+      <c r="E727">
+        <v>30</v>
+      </c>
+      <c r="F727">
+        <v>28</v>
+      </c>
+      <c r="G727">
+        <v>48</v>
+      </c>
+      <c r="H727">
+        <v>36</v>
+      </c>
+      <c r="I727">
+        <v>37</v>
+      </c>
+      <c r="J727">
+        <v>35</v>
+      </c>
+      <c r="K727">
+        <v>32</v>
+      </c>
+      <c r="L727">
+        <v>32</v>
+      </c>
+      <c r="M727">
+        <v>33</v>
+      </c>
+      <c r="N727">
+        <v>36</v>
+      </c>
+      <c r="O727">
+        <v>38</v>
+      </c>
+      <c r="P727">
+        <v>29</v>
+      </c>
+      <c r="Q727">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="R727">
+        <v>35.8</v>
+      </c>
+      <c r="S727">
+        <v>32.46321275452881</v>
+      </c>
+      <c r="T727">
+        <v>33.79583579872627</v>
       </c>
     </row>
   </sheetData>
